--- a/docs/rebar_splice/鉄筋継手問題集.xlsx
+++ b/docs/rebar_splice/鉄筋継手問題集.xlsx
@@ -241,6 +241,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -271,6 +274,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -279,6 +285,66 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8191500" cy="3495675"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8191500" cy="3352800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -301,6 +367,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1136,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1562,8 +1631,15 @@
         </is>
       </c>
     </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>■ 補足図（理解の整理）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A3:G3"/>
@@ -1573,9 +1649,11 @@
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A29:G29"/>
     <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A31:H31"/>
     <mergeCell ref="A28:G28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1585,7 +1663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1824,19 +1902,28 @@
         </is>
       </c>
     </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>■ 補足図（理解の整理）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A27:H27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
